--- a/docs/Decodifiche/108_dec_dati_adozione_minore_internazionale.xlsx
+++ b/docs/Decodifiche/108_dec_dati_adozione_minore_internazionale.xlsx
@@ -44,7 +44,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Atto di nascita con nuove generalità</t>
+    <t>Atto di nascita con nuove generalità - Atto Adozione con con dati precedenti all'adozione</t>
   </si>
   <si>
     <t>3</t>
@@ -113,7 +113,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="3.02734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="80.46484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.55859375" customWidth="true" bestFit="true"/>
